--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736E3C1A-EA95-48A9-8AA1-9887615EF343}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC74845F-52CC-4D47-8A1B-9553F640C4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构转产表" sheetId="1" r:id="rId1"/>
@@ -310,7 +310,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -340,13 +340,6 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -408,6 +401,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -461,58 +471,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -833,370 +843,682 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="9.25" customWidth="1"/>
-    <col min="6" max="9" width="7.875" customWidth="1"/>
+    <col min="6" max="9" width="7.83203125" customWidth="1"/>
     <col min="10" max="40" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:40" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6"/>
-      <c r="Z1" s="7" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="Z1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AH1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:40" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:40" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
-      <c r="AL2" s="16"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="16"/>
-    </row>
-    <row r="3" spans="1:40" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="11">
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="13"/>
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="13"/>
+    </row>
+    <row r="3" spans="1:40" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="15">
         <v>1</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="15">
         <v>2</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="15">
         <v>3</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="15">
         <v>4</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="15">
         <v>5</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="15">
         <v>6</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="15">
         <v>7</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="15">
         <v>8</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="15">
         <v>9</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="15">
         <v>10</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="15">
         <v>11</v>
       </c>
-      <c r="U3" s="11">
+      <c r="U3" s="15">
         <v>12</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="15">
         <v>13</v>
       </c>
-      <c r="W3" s="11">
+      <c r="W3" s="15">
         <v>14</v>
       </c>
-      <c r="X3" s="11">
+      <c r="X3" s="15">
         <v>15</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Y3" s="15">
         <v>16</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="Z3" s="15">
         <v>17</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AA3" s="15">
         <v>18</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AB3" s="15">
         <v>19</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AC3" s="15">
         <v>20</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AD3" s="15">
         <v>21</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AE3" s="15">
         <v>22</v>
       </c>
-      <c r="AF3" s="11">
+      <c r="AF3" s="15">
         <v>23</v>
       </c>
-      <c r="AG3" s="11">
+      <c r="AG3" s="15">
         <v>24</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AH3" s="15">
         <v>25</v>
       </c>
-      <c r="AI3" s="11">
+      <c r="AI3" s="15">
         <v>26</v>
       </c>
-      <c r="AJ3" s="11">
+      <c r="AJ3" s="15">
         <v>27</v>
       </c>
-      <c r="AK3" s="11">
+      <c r="AK3" s="15">
         <v>28</v>
       </c>
-      <c r="AL3" s="11">
+      <c r="AL3" s="15">
         <v>29</v>
       </c>
-      <c r="AM3" s="11">
+      <c r="AM3" s="15">
         <v>30</v>
       </c>
-      <c r="AN3" s="11">
+      <c r="AN3" s="15">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="T4" s="18" t="s">
+      <c r="T4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="18" t="s">
+      <c r="U4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="W4" s="18" t="s">
+      <c r="W4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="18" t="s">
+      <c r="X4" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Y4" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AC4" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="AD4" s="18" t="s">
+      <c r="AD4" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="AE4" s="18" t="s">
+      <c r="AE4" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="AF4" s="18" t="s">
+      <c r="AF4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" s="18" t="s">
+      <c r="AG4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="AH4" s="18" t="s">
+      <c r="AH4" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="18" t="s">
+      <c r="AI4" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="18" t="s">
+      <c r="AJ4" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AK4" s="18" t="s">
+      <c r="AK4" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="AL4" s="18" t="s">
+      <c r="AL4" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AM4" s="18" t="s">
+      <c r="AM4" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AN4" s="18" t="s">
+      <c r="AN4" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C6" s="2" t="s">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="17"/>
+      <c r="AH5" s="17"/>
+      <c r="AI5" s="17"/>
+      <c r="AJ5" s="17"/>
+      <c r="AK5" s="17"/>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="17"/>
+      <c r="AN5" s="17"/>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C7" s="1" t="s">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="17"/>
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="17"/>
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="17"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="17"/>
+      <c r="AN6" s="17"/>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="18" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C8" s="12" t="s">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="17"/>
+      <c r="AN7" s="17"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C10" s="2" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="17"/>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="17"/>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C11" s="1" t="s">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="17"/>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="18" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="C12" s="1" t="s">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="18" t="s">
         <v>73</v>
       </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1220,13 +1542,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09566F27-C80A-412A-A430-D5D9F6DA5938}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1234,7 +1556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1250,7 +1572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1258,7 +1580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1266,7 +1588,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1274,7 +1596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1282,7 +1604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1290,7 +1612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1298,7 +1620,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1306,7 +1628,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1314,7 +1636,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1322,7 +1644,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1330,7 +1652,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5</v>
       </c>
@@ -1338,7 +1660,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1346,7 +1668,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1354,7 +1676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>8</v>
       </c>
@@ -1362,7 +1684,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>9</v>
       </c>
@@ -1370,7 +1692,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10</v>
       </c>
@@ -1378,7 +1700,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>11</v>
       </c>
@@ -1386,7 +1708,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>12</v>
       </c>
@@ -1394,7 +1716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>13</v>
       </c>
@@ -1402,7 +1724,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>14</v>
       </c>
@@ -1410,7 +1732,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>15</v>
       </c>
@@ -1418,7 +1740,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1426,7 +1748,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>17</v>
       </c>
@@ -1434,7 +1756,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>18</v>
       </c>
@@ -1442,7 +1764,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>19</v>
       </c>
@@ -1450,7 +1772,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>20</v>
       </c>
@@ -1458,7 +1780,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>21</v>
       </c>
@@ -1466,7 +1788,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>22</v>
       </c>
@@ -1474,7 +1796,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>23</v>
       </c>
@@ -1482,7 +1804,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>24</v>
       </c>
@@ -1490,7 +1812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>25</v>
       </c>
@@ -1498,7 +1820,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>26</v>
       </c>
@@ -1506,7 +1828,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>27</v>
       </c>
@@ -1514,7 +1836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>28</v>
       </c>
@@ -1522,7 +1844,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>29</v>
       </c>
@@ -1530,7 +1852,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>30</v>
       </c>
@@ -1538,7 +1860,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>31</v>
       </c>
@@ -1555,142 +1877,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786B80D1-0B96-4ADE-83D0-F51287771B06}">
   <dimension ref="A1:AN5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:40" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:40" ht="23" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="11">
+      <c r="J1" s="8">
         <v>1</v>
       </c>
-      <c r="K1" s="11">
+      <c r="K1" s="8">
         <v>2</v>
       </c>
-      <c r="L1" s="11">
+      <c r="L1" s="8">
         <v>3</v>
       </c>
-      <c r="M1" s="11">
+      <c r="M1" s="8">
         <v>4</v>
       </c>
-      <c r="N1" s="11">
+      <c r="N1" s="8">
         <v>5</v>
       </c>
-      <c r="O1" s="11">
+      <c r="O1" s="8">
         <v>6</v>
       </c>
-      <c r="P1" s="11">
+      <c r="P1" s="8">
         <v>7</v>
       </c>
-      <c r="Q1" s="11">
+      <c r="Q1" s="8">
         <v>8</v>
       </c>
-      <c r="R1" s="11">
+      <c r="R1" s="8">
         <v>9</v>
       </c>
-      <c r="S1" s="11">
+      <c r="S1" s="8">
         <v>10</v>
       </c>
-      <c r="T1" s="11">
+      <c r="T1" s="8">
         <v>11</v>
       </c>
-      <c r="U1" s="11">
+      <c r="U1" s="8">
         <v>12</v>
       </c>
-      <c r="V1" s="11">
+      <c r="V1" s="8">
         <v>13</v>
       </c>
-      <c r="W1" s="11">
+      <c r="W1" s="8">
         <v>14</v>
       </c>
-      <c r="X1" s="11">
+      <c r="X1" s="8">
         <v>15</v>
       </c>
-      <c r="Y1" s="11">
+      <c r="Y1" s="8">
         <v>16</v>
       </c>
-      <c r="Z1" s="11">
+      <c r="Z1" s="8">
         <v>17</v>
       </c>
-      <c r="AA1" s="11">
+      <c r="AA1" s="8">
         <v>18</v>
       </c>
-      <c r="AB1" s="11">
+      <c r="AB1" s="8">
         <v>19</v>
       </c>
-      <c r="AC1" s="11">
+      <c r="AC1" s="8">
         <v>20</v>
       </c>
-      <c r="AD1" s="11">
+      <c r="AD1" s="8">
         <v>21</v>
       </c>
-      <c r="AE1" s="11">
+      <c r="AE1" s="8">
         <v>22</v>
       </c>
-      <c r="AF1" s="11">
+      <c r="AF1" s="8">
         <v>23</v>
       </c>
-      <c r="AG1" s="11">
+      <c r="AG1" s="8">
         <v>24</v>
       </c>
-      <c r="AH1" s="11">
+      <c r="AH1" s="8">
         <v>25</v>
       </c>
-      <c r="AI1" s="11">
+      <c r="AI1" s="8">
         <v>26</v>
       </c>
-      <c r="AJ1" s="11">
+      <c r="AJ1" s="8">
         <v>27</v>
       </c>
-      <c r="AK1" s="11">
+      <c r="AK1" s="8">
         <v>28</v>
       </c>
-      <c r="AL1" s="11">
+      <c r="AL1" s="8">
         <v>29</v>
       </c>
-      <c r="AM1" s="11">
+      <c r="AM1" s="8">
         <v>30</v>
       </c>
-      <c r="AN1" s="11">
+      <c r="AN1" s="8">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC74845F-52CC-4D47-8A1B-9553F640C4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B91D7C-8D72-42AD-80FB-B5F1F2CF9BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="115">
   <si>
     <t>成型机台</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,6 +301,126 @@
   <si>
     <t>{.changeCount}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.cxMachineCodeA}</t>
+  </si>
+  <si>
+    <t>{.cxMachineTypeCodeA}</t>
+  </si>
+  <si>
+    <t>{.structureNameA}</t>
+  </si>
+  <si>
+    <t>{.structureTypeA}</t>
+  </si>
+  <si>
+    <t>{.netQtyA}</t>
+  </si>
+  <si>
+    <t>{.totalQtyA}</t>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
+  </si>
+  <si>
+    <t>{.allotDaysA}</t>
+  </si>
+  <si>
+    <t>{.maxLhMachineCountA}</t>
+  </si>
+  <si>
+    <t>{.day1A}</t>
+  </si>
+  <si>
+    <t>{.day2A}</t>
+  </si>
+  <si>
+    <t>{.day3A}</t>
+  </si>
+  <si>
+    <t>{.day4A}</t>
+  </si>
+  <si>
+    <t>{.day5A}</t>
+  </si>
+  <si>
+    <t>{.day6A}</t>
+  </si>
+  <si>
+    <t>{.day7A}</t>
+  </si>
+  <si>
+    <t>{.day8A}</t>
+  </si>
+  <si>
+    <t>{.day9A}</t>
+  </si>
+  <si>
+    <t>{.day10A}</t>
+  </si>
+  <si>
+    <t>{.day11A}</t>
+  </si>
+  <si>
+    <t>{.day12A}</t>
+  </si>
+  <si>
+    <t>{.day13A}</t>
+  </si>
+  <si>
+    <t>{.day14A}</t>
+  </si>
+  <si>
+    <t>{.day15A}</t>
+  </si>
+  <si>
+    <t>{.day16A}</t>
+  </si>
+  <si>
+    <t>{.day17A}</t>
+  </si>
+  <si>
+    <t>{.day18A}</t>
+  </si>
+  <si>
+    <t>{.day19A}</t>
+  </si>
+  <si>
+    <t>{.day20A}</t>
+  </si>
+  <si>
+    <t>{.day21A}</t>
+  </si>
+  <si>
+    <t>{.day22A}</t>
+  </si>
+  <si>
+    <t>{.day23A}</t>
+  </si>
+  <si>
+    <t>{.day24A}</t>
+  </si>
+  <si>
+    <t>{.day25A}</t>
+  </si>
+  <si>
+    <t>{.day26A}</t>
+  </si>
+  <si>
+    <t>{.day27A}</t>
+  </si>
+  <si>
+    <t>{.day28A}</t>
+  </si>
+  <si>
+    <t>{.day29A}</t>
+  </si>
+  <si>
+    <t>{.day30A}</t>
+  </si>
+  <si>
+    <t>{.day31A}</t>
   </si>
 </sst>
 </file>
@@ -504,15 +624,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -522,6 +633,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -872,666 +992,788 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:40" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="W2" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="X2" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y2" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z2" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA2" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI2" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL2" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AN2" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-      <c r="AH2" s="13"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
-      <c r="AL2" s="13"/>
-      <c r="AM2" s="13"/>
-      <c r="AN2" s="13"/>
-    </row>
-    <row r="3" spans="1:40" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="15">
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="17"/>
+      <c r="AM3" s="17"/>
+      <c r="AN3" s="17"/>
+    </row>
+    <row r="4" spans="1:40" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="12">
         <v>1</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K4" s="12">
         <v>2</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L4" s="12">
         <v>3</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M4" s="12">
         <v>4</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N4" s="12">
         <v>5</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O4" s="12">
         <v>6</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P4" s="12">
         <v>7</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q4" s="12">
         <v>8</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R4" s="12">
         <v>9</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S4" s="12">
         <v>10</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T4" s="12">
         <v>11</v>
       </c>
-      <c r="U3" s="15">
+      <c r="U4" s="12">
         <v>12</v>
       </c>
-      <c r="V3" s="15">
+      <c r="V4" s="12">
         <v>13</v>
       </c>
-      <c r="W3" s="15">
+      <c r="W4" s="12">
         <v>14</v>
       </c>
-      <c r="X3" s="15">
+      <c r="X4" s="12">
         <v>15</v>
       </c>
-      <c r="Y3" s="15">
+      <c r="Y4" s="12">
         <v>16</v>
       </c>
-      <c r="Z3" s="15">
+      <c r="Z4" s="12">
         <v>17</v>
       </c>
-      <c r="AA3" s="15">
+      <c r="AA4" s="12">
         <v>18</v>
       </c>
-      <c r="AB3" s="15">
+      <c r="AB4" s="12">
         <v>19</v>
       </c>
-      <c r="AC3" s="15">
+      <c r="AC4" s="12">
         <v>20</v>
       </c>
-      <c r="AD3" s="15">
+      <c r="AD4" s="12">
         <v>21</v>
       </c>
-      <c r="AE3" s="15">
+      <c r="AE4" s="12">
         <v>22</v>
       </c>
-      <c r="AF3" s="15">
+      <c r="AF4" s="12">
         <v>23</v>
       </c>
-      <c r="AG3" s="15">
+      <c r="AG4" s="12">
         <v>24</v>
       </c>
-      <c r="AH3" s="15">
+      <c r="AH4" s="12">
         <v>25</v>
       </c>
-      <c r="AI3" s="15">
+      <c r="AI4" s="12">
         <v>26</v>
       </c>
-      <c r="AJ3" s="15">
+      <c r="AJ4" s="12">
         <v>27</v>
       </c>
-      <c r="AK3" s="15">
+      <c r="AK4" s="12">
         <v>28</v>
       </c>
-      <c r="AL3" s="15">
+      <c r="AL4" s="12">
         <v>29</v>
       </c>
-      <c r="AM3" s="15">
+      <c r="AM4" s="12">
         <v>30</v>
       </c>
-      <c r="AN3" s="15">
+      <c r="AN4" s="12">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+    <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="L5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="O5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="P5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="16" t="s">
+      <c r="Q5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="16" t="s">
+      <c r="R5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="16" t="s">
+      <c r="U5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="V4" s="16" t="s">
+      <c r="V5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="W4" s="16" t="s">
+      <c r="W5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="16" t="s">
+      <c r="X5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="Y4" s="16" t="s">
+      <c r="Y5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="Z4" s="16" t="s">
+      <c r="Z5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="16" t="s">
+      <c r="AA5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" s="16" t="s">
+      <c r="AB5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AC4" s="16" t="s">
+      <c r="AC5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AD4" s="16" t="s">
+      <c r="AD5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="AE4" s="16" t="s">
+      <c r="AE5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AF4" s="16" t="s">
+      <c r="AF5" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" s="16" t="s">
+      <c r="AG5" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="AH4" s="16" t="s">
+      <c r="AH5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AI4" s="16" t="s">
+      <c r="AI5" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AJ4" s="16" t="s">
+      <c r="AJ5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AK4" s="16" t="s">
+      <c r="AK5" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="AL4" s="16" t="s">
+      <c r="AL5" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AM4" s="16" t="s">
+      <c r="AM5" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AN4" s="16" t="s">
+      <c r="AN5" s="13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="17"/>
-      <c r="AL5" s="17"/>
-      <c r="AM5" s="17"/>
-      <c r="AN5" s="17"/>
-    </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="17"/>
-      <c r="AL6" s="17"/>
-      <c r="AM6" s="17"/>
-      <c r="AN6" s="17"/>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="14"/>
+      <c r="AM7" s="14"/>
+      <c r="AN7" s="14"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="17"/>
-      <c r="AK7" s="17"/>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="17"/>
-      <c r="AN7" s="17"/>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="14"/>
+      <c r="AL8" s="14"/>
+      <c r="AM8" s="14"/>
+      <c r="AN8" s="14"/>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
-      <c r="AN8" s="17"/>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="17"/>
-      <c r="AM9" s="17"/>
-      <c r="AN9" s="17"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="14"/>
+      <c r="AN9" s="14"/>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="14"/>
+      <c r="AJ10" s="14"/>
+      <c r="AK10" s="14"/>
+      <c r="AL10" s="14"/>
+      <c r="AM10" s="14"/>
+      <c r="AN10" s="14"/>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="17"/>
-      <c r="AM10" s="17"/>
-      <c r="AN10" s="17"/>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18" t="s">
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+      <c r="AM11" s="14"/>
+      <c r="AN11" s="14"/>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D12" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
-      <c r="AN11" s="17"/>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18" t="s">
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="14"/>
+      <c r="AN12" s="14"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D13" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
-      <c r="AN12" s="17"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:AN2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:AN3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED45AE7-F592-4ABA-9B97-CD3501549C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF6317F-D0B2-4888-AC28-8A158880D2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,6 +220,146 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{changeAllCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.machineCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{proSizeChangeCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{structureChangeCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.changeCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.cxMachineCodeA}</t>
+  </si>
+  <si>
+    <t>{.cxMachineTypeCodeA}</t>
+  </si>
+  <si>
+    <t>{.structureNameA}</t>
+  </si>
+  <si>
+    <t>{.structureTypeA}</t>
+  </si>
+  <si>
+    <t>{.netQtyA}</t>
+  </si>
+  <si>
+    <t>{.totalQtyA}</t>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
+  </si>
+  <si>
+    <t>{.allotDaysA}</t>
+  </si>
+  <si>
+    <t>{.maxLhMachineCountA}</t>
+  </si>
+  <si>
+    <t>{.day1A}</t>
+  </si>
+  <si>
+    <t>{.day2A}</t>
+  </si>
+  <si>
+    <t>{.day3A}</t>
+  </si>
+  <si>
+    <t>{.day4A}</t>
+  </si>
+  <si>
+    <t>{.day5A}</t>
+  </si>
+  <si>
+    <t>{.day6A}</t>
+  </si>
+  <si>
+    <t>{.day7A}</t>
+  </si>
+  <si>
+    <t>{.day8A}</t>
+  </si>
+  <si>
+    <t>{.day9A}</t>
+  </si>
+  <si>
+    <t>{.day10A}</t>
+  </si>
+  <si>
+    <t>{.day11A}</t>
+  </si>
+  <si>
+    <t>{.day12A}</t>
+  </si>
+  <si>
+    <t>{.day13A}</t>
+  </si>
+  <si>
+    <t>{.day14A}</t>
+  </si>
+  <si>
+    <t>{.day15A}</t>
+  </si>
+  <si>
+    <t>{.day16A}</t>
+  </si>
+  <si>
+    <t>{.day17A}</t>
+  </si>
+  <si>
+    <t>{.day18A}</t>
+  </si>
+  <si>
+    <t>{.day19A}</t>
+  </si>
+  <si>
+    <t>{.day20A}</t>
+  </si>
+  <si>
+    <t>{.day21A}</t>
+  </si>
+  <si>
+    <t>{.day22A}</t>
+  </si>
+  <si>
+    <t>{.day23A}</t>
+  </si>
+  <si>
+    <t>{.day24A}</t>
+  </si>
+  <si>
+    <t>{.day25A}</t>
+  </si>
+  <si>
+    <t>{.day26A}</t>
+  </si>
+  <si>
+    <t>{.day27A}</t>
+  </si>
+  <si>
+    <t>{.day28A}</t>
+  </si>
+  <si>
+    <t>{.day29A}</t>
+  </si>
+  <si>
+    <t>{.day30A}</t>
+  </si>
+  <si>
+    <t>{.day31A}</t>
+  </si>
+  <si>
     <r>
       <t>{factoryName}</t>
     </r>
@@ -227,7 +367,7 @@
       <rPr>
         <b/>
         <u/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <family val="3"/>
@@ -239,7 +379,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color indexed="8"/>
         <rFont val="等线"/>
         <family val="3"/>
@@ -250,146 +390,6 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>{changeAllCount}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.machineCount}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{proSizeChangeCount}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{structureChangeCount}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.changeCount}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.cxMachineCodeA}</t>
-  </si>
-  <si>
-    <t>{.cxMachineTypeCodeA}</t>
-  </si>
-  <si>
-    <t>{.structureNameA}</t>
-  </si>
-  <si>
-    <t>{.structureTypeA}</t>
-  </si>
-  <si>
-    <t>{.netQtyA}</t>
-  </si>
-  <si>
-    <t>{.totalQtyA}</t>
-  </si>
-  <si>
-    <t>{.differenceQtyA}</t>
-  </si>
-  <si>
-    <t>{.allotDaysA}</t>
-  </si>
-  <si>
-    <t>{.maxLhMachineCountA}</t>
-  </si>
-  <si>
-    <t>{.day1A}</t>
-  </si>
-  <si>
-    <t>{.day2A}</t>
-  </si>
-  <si>
-    <t>{.day3A}</t>
-  </si>
-  <si>
-    <t>{.day4A}</t>
-  </si>
-  <si>
-    <t>{.day5A}</t>
-  </si>
-  <si>
-    <t>{.day6A}</t>
-  </si>
-  <si>
-    <t>{.day7A}</t>
-  </si>
-  <si>
-    <t>{.day8A}</t>
-  </si>
-  <si>
-    <t>{.day9A}</t>
-  </si>
-  <si>
-    <t>{.day10A}</t>
-  </si>
-  <si>
-    <t>{.day11A}</t>
-  </si>
-  <si>
-    <t>{.day12A}</t>
-  </si>
-  <si>
-    <t>{.day13A}</t>
-  </si>
-  <si>
-    <t>{.day14A}</t>
-  </si>
-  <si>
-    <t>{.day15A}</t>
-  </si>
-  <si>
-    <t>{.day16A}</t>
-  </si>
-  <si>
-    <t>{.day17A}</t>
-  </si>
-  <si>
-    <t>{.day18A}</t>
-  </si>
-  <si>
-    <t>{.day19A}</t>
-  </si>
-  <si>
-    <t>{.day20A}</t>
-  </si>
-  <si>
-    <t>{.day21A}</t>
-  </si>
-  <si>
-    <t>{.day22A}</t>
-  </si>
-  <si>
-    <t>{.day23A}</t>
-  </si>
-  <si>
-    <t>{.day24A}</t>
-  </si>
-  <si>
-    <t>{.day25A}</t>
-  </si>
-  <si>
-    <t>{.day26A}</t>
-  </si>
-  <si>
-    <t>{.day27A}</t>
-  </si>
-  <si>
-    <t>{.day28A}</t>
-  </si>
-  <si>
-    <t>{.day29A}</t>
-  </si>
-  <si>
-    <t>{.day30A}</t>
-  </si>
-  <si>
-    <t>{.day31A}</t>
-  </si>
 </sst>
 </file>
 
@@ -398,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -414,44 +414,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -483,7 +447,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
       <family val="3"/>
@@ -492,7 +457,25 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -556,50 +539,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -931,793 +914,823 @@
     <col min="10" max="40" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="Z1" s="5" t="s">
+    <row r="1" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
     </row>
-    <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="Q2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="R2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="S2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="X2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="Y2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AF2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AG2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AK2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AL2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AM2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AN2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" s="12" t="s">
-        <v>104</v>
-      </c>
     </row>
-    <row r="3" spans="1:40" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:40" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="15"/>
+      <c r="AH3" s="15"/>
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15"/>
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15"/>
     </row>
-    <row r="4" spans="1:40" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="9">
+    <row r="4" spans="1:40" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="4">
         <v>2</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="4">
         <v>3</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="4">
         <v>4</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="4">
         <v>5</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="4">
         <v>6</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="4">
         <v>7</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="Q4" s="4">
         <v>8</v>
       </c>
-      <c r="R4" s="9">
+      <c r="R4" s="4">
         <v>9</v>
       </c>
-      <c r="S4" s="9">
+      <c r="S4" s="4">
         <v>10</v>
       </c>
-      <c r="T4" s="9">
+      <c r="T4" s="4">
         <v>11</v>
       </c>
-      <c r="U4" s="9">
+      <c r="U4" s="4">
         <v>12</v>
       </c>
-      <c r="V4" s="9">
+      <c r="V4" s="4">
         <v>13</v>
       </c>
-      <c r="W4" s="9">
+      <c r="W4" s="4">
         <v>14</v>
       </c>
-      <c r="X4" s="9">
+      <c r="X4" s="4">
         <v>15</v>
       </c>
-      <c r="Y4" s="9">
+      <c r="Y4" s="4">
         <v>16</v>
       </c>
-      <c r="Z4" s="9">
+      <c r="Z4" s="4">
         <v>17</v>
       </c>
-      <c r="AA4" s="9">
+      <c r="AA4" s="4">
         <v>18</v>
       </c>
-      <c r="AB4" s="9">
+      <c r="AB4" s="4">
         <v>19</v>
       </c>
-      <c r="AC4" s="9">
+      <c r="AC4" s="4">
         <v>20</v>
       </c>
-      <c r="AD4" s="9">
+      <c r="AD4" s="4">
         <v>21</v>
       </c>
-      <c r="AE4" s="9">
+      <c r="AE4" s="4">
         <v>22</v>
       </c>
-      <c r="AF4" s="9">
+      <c r="AF4" s="4">
         <v>23</v>
       </c>
-      <c r="AG4" s="9">
+      <c r="AG4" s="4">
         <v>24</v>
       </c>
-      <c r="AH4" s="9">
+      <c r="AH4" s="4">
         <v>25</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AI4" s="4">
         <v>26</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AJ4" s="4">
         <v>27</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AK4" s="4">
         <v>28</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AL4" s="4">
         <v>29</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AM4" s="4">
         <v>30</v>
       </c>
-      <c r="AN4" s="9">
+      <c r="AN4" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="P5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="16" t="s">
+      <c r="R5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="16" t="s">
+      <c r="S5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="T5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="U5" s="16" t="s">
+      <c r="U5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="V5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="W5" s="16" t="s">
+      <c r="W5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="X5" s="16" t="s">
+      <c r="X5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="Y5" s="16" t="s">
+      <c r="Y5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="Z5" s="16" t="s">
+      <c r="Z5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AA5" s="16" t="s">
+      <c r="AA5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AB5" s="16" t="s">
+      <c r="AB5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="16" t="s">
+      <c r="AC5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AD5" s="16" t="s">
+      <c r="AD5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AE5" s="16" t="s">
+      <c r="AE5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AF5" s="16" t="s">
+      <c r="AF5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AG5" s="16" t="s">
+      <c r="AG5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AH5" s="16" t="s">
+      <c r="AH5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AI5" s="16" t="s">
+      <c r="AI5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AJ5" s="16" t="s">
+      <c r="AJ5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AK5" s="16" t="s">
+      <c r="AK5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AL5" s="16" t="s">
+      <c r="AL5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AM5" s="16" t="s">
+      <c r="AM5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AN5" s="16" t="s">
+      <c r="AN5" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="10"/>
-      <c r="AG6" s="10"/>
-      <c r="AH6" s="10"/>
-      <c r="AI6" s="10"/>
-      <c r="AJ6" s="10"/>
-      <c r="AK6" s="10"/>
-      <c r="AL6" s="10"/>
-      <c r="AM6" s="10"/>
-      <c r="AN6" s="10"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="7"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
-      <c r="AI7" s="10"/>
-      <c r="AJ7" s="10"/>
-      <c r="AK7" s="10"/>
-      <c r="AL7" s="10"/>
-      <c r="AM7" s="10"/>
-      <c r="AN7" s="10"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
-      <c r="AI8" s="10"/>
-      <c r="AJ8" s="10"/>
-      <c r="AK8" s="10"/>
-      <c r="AL8" s="10"/>
-      <c r="AM8" s="10"/>
-      <c r="AN8" s="10"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
-      <c r="AB9" s="10"/>
-      <c r="AC9" s="10"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="10"/>
-      <c r="AF9" s="10"/>
-      <c r="AG9" s="10"/>
-      <c r="AH9" s="10"/>
-      <c r="AI9" s="10"/>
-      <c r="AJ9" s="10"/>
-      <c r="AK9" s="10"/>
-      <c r="AL9" s="10"/>
-      <c r="AM9" s="10"/>
-      <c r="AN9" s="10"/>
+      <c r="D9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="7"/>
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="7"/>
+      <c r="AL9" s="7"/>
+      <c r="AM9" s="7"/>
+      <c r="AN9" s="7"/>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
-      <c r="AI10" s="10"/>
-      <c r="AJ10" s="10"/>
-      <c r="AK10" s="10"/>
-      <c r="AL10" s="10"/>
-      <c r="AM10" s="10"/>
-      <c r="AN10" s="10"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="7"/>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="7"/>
+      <c r="AM10" s="7"/>
+      <c r="AN10" s="7"/>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
-      <c r="AI11" s="10"/>
-      <c r="AJ11" s="10"/>
-      <c r="AK11" s="10"/>
-      <c r="AL11" s="10"/>
-      <c r="AM11" s="10"/>
-      <c r="AN11" s="10"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
-      <c r="AJ12" s="10"/>
-      <c r="AK12" s="10"/>
-      <c r="AL12" s="10"/>
-      <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="7"/>
+      <c r="AN12" s="7"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
-      <c r="AF13" s="10"/>
-      <c r="AG13" s="10"/>
-      <c r="AH13" s="10"/>
-      <c r="AI13" s="10"/>
-      <c r="AJ13" s="10"/>
-      <c r="AK13" s="10"/>
-      <c r="AL13" s="10"/>
-      <c r="AM13" s="10"/>
-      <c r="AN13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="7"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="7"/>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF6317F-D0B2-4888-AC28-8A158880D2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8CD513-A0A3-476C-B5DF-127B0CAACA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,11 +67,6 @@
   </si>
   <si>
     <t xml:space="preserve">在机天数 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>硫化机
-应数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -388,6 +383,11 @@
       </rPr>
       <t xml:space="preserve"> 成型机结构转产表</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫化机
+数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +572,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -583,6 +582,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -916,7 +916,7 @@
   <sheetData>
     <row r="1" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -943,7 +943,7 @@
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="7"/>
       <c r="AB1" s="7"/>
@@ -953,7 +953,7 @@
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
       <c r="AH1" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AI1" s="7"/>
       <c r="AJ1" s="7"/>
@@ -963,199 +963,199 @@
       <c r="AN1" s="7"/>
     </row>
     <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="Q2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="R2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="S2" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="X2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="Y2" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AF2" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AG2" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AK2" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AL2" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AM2" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AN2" s="16" t="s">
         <v>102</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:40" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="15" t="s">
+      <c r="I3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
-      <c r="AH3" s="15"/>
-      <c r="AI3" s="15"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
     </row>
     <row r="4" spans="1:40" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="4">
         <v>1</v>
       </c>
@@ -1251,125 +1251,125 @@
       </c>
     </row>
     <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="L5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="M5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="N5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="O5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="P5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="Q5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="R5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="S5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="T5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="U5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="V5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="W5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="X5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="Y5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Z5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="AA5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AB5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AB5" s="13" t="s">
+      <c r="AC5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="13" t="s">
+      <c r="AD5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="AD5" s="13" t="s">
+      <c r="AE5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AE5" s="13" t="s">
+      <c r="AF5" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AF5" s="13" t="s">
+      <c r="AG5" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="AG5" s="13" t="s">
+      <c r="AH5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AH5" s="13" t="s">
+      <c r="AI5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AI5" s="13" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="AJ5" s="13" t="s">
+      <c r="AK5" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="AK5" s="13" t="s">
+      <c r="AL5" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="AL5" s="13" t="s">
+      <c r="AM5" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="AM5" s="13" t="s">
+      <c r="AN5" s="12" t="s">
         <v>54</v>
-      </c>
-      <c r="AN5" s="13" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
@@ -1421,7 +1421,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1464,10 +1464,10 @@
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -1510,10 +1510,10 @@
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1601,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -1647,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1693,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8CD513-A0A3-476C-B5DF-127B0CAACA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC65660-9F36-4EA0-8549-BD695893108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,71 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
-  <si>
-    <t>成型机台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际排产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未排产量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每日实际排产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英寸交替</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单机台切换次数统计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交替类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构切换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">在机天数 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产净需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计切换次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -207,14 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需求计划版本：{monthPlanVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{changeAllCount}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -355,39 +283,79 @@
     <t>{.day31A}</t>
   </si>
   <si>
-    <r>
-      <t>{factoryName}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color indexed="8"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 成型机结构转产表</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>硫化机
-数量</t>
+    <t>{title}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cxMachineCode}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cxMachineTypeCode}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{structureName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{structureType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{netQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{differenceQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{allotDays}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{maxLhMachineCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dailyproductionQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{changeSingleCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{changeMachineCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalChangeCount}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{changeType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{proSizeChangeCountLabel}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{structureChangeCountLabel}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{monthPlanVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{productionVersion}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -398,7 +366,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -450,16 +418,6 @@
       <b/>
       <sz val="9"/>
       <color indexed="8"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -535,7 +493,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -557,22 +515,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -582,7 +545,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -916,7 +881,7 @@
   <sheetData>
     <row r="1" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -943,7 +908,7 @@
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="9" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="AA1" s="7"/>
       <c r="AB1" s="7"/>
@@ -953,7 +918,7 @@
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
       <c r="AH1" s="7" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="AI1" s="7"/>
       <c r="AJ1" s="7"/>
@@ -963,199 +928,199 @@
       <c r="AN1" s="7"/>
     </row>
     <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="S2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="T2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="U2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="V2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="W2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="X2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="Y2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="Z2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="AA2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="AB2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="AC2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="AD2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="AE2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="AF2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="AG2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="AH2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="AI2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="AJ2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="AK2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="AL2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="AM2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="16" t="s">
+      <c r="AN2" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="W2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="X2" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y2" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA2" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC2" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD2" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE2" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF2" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="AI2" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ2" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK2" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL2" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM2" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="AN2" s="16" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:40" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
+      <c r="A3" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="15"/>
+      <c r="AH3" s="15"/>
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15"/>
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15"/>
     </row>
     <row r="4" spans="1:40" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="4">
         <v>1</v>
       </c>
@@ -1252,176 +1217,176 @@
     </row>
     <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="12" t="s">
+      <c r="S5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="T5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="U5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="W5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="Y5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="AC5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="AD5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="AE5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="AG5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="AH5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="AI5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="AK5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="AL5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="AM5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="AN5" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF5" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG5" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH5" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI5" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ5" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK5" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL5" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM5" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN5" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
-      <c r="AE6" s="7"/>
-      <c r="AF6" s="7"/>
-      <c r="AG6" s="7"/>
-      <c r="AH6" s="7"/>
-      <c r="AI6" s="7"/>
-      <c r="AJ6" s="7"/>
-      <c r="AK6" s="7"/>
-      <c r="AL6" s="7"/>
-      <c r="AM6" s="7"/>
-      <c r="AN6" s="7"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="13"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1464,10 +1429,10 @@
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -1510,10 +1475,10 @@
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1598,10 +1563,10 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -1644,10 +1609,10 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1690,10 +1655,10 @@
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="10" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC65660-9F36-4EA0-8549-BD695893108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C269B7-C6AC-471F-9A5D-D34FE3735CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -31,9 +31,6 @@
     <t>{.structureType}</t>
   </si>
   <si>
-    <t>{.netQty}</t>
-  </si>
-  <si>
     <t>{.totalQty}</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
     <t>{.structureTypeA}</t>
   </si>
   <si>
-    <t>{.netQtyA}</t>
-  </si>
-  <si>
     <t>{.totalQtyA}</t>
   </si>
   <si>
@@ -303,10 +297,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{netQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{totalQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -356,6 +346,30 @@
   </si>
   <si>
     <t>{productionVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lossQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lossQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lossQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unPostponeNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{unPostponeNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unPostponeNetQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,6 +550,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -544,9 +561,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,31 +881,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="9.25" customWidth="1"/>
-    <col min="6" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="40" width="4.75" customWidth="1"/>
+    <col min="5" max="6" width="9.25" customWidth="1"/>
+    <col min="7" max="10" width="7.83203125" customWidth="1"/>
+    <col min="11" max="41" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
+      <c r="F1" s="7"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="7"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="6"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
@@ -907,320 +921,328 @@
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
-      <c r="Z1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
-      <c r="AH1" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
       <c r="AM1" s="7"/>
       <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
     </row>
-    <row r="2" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="I2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="J2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="K2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="L2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="M2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="N2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="O2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="P2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="Q2" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="R2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="S2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="T2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="U2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="V2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="W2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="X2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="Y2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="Z2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="17" t="s">
+      <c r="AA2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" s="17" t="s">
+      <c r="AB2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" s="17" t="s">
+      <c r="AC2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" s="17" t="s">
+      <c r="AD2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" s="17" t="s">
+      <c r="AE2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" s="17" t="s">
+      <c r="AF2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" s="17" t="s">
+      <c r="AG2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" s="17" t="s">
+      <c r="AH2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" s="17" t="s">
+      <c r="AI2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" s="17" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AK2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" s="17" t="s">
+      <c r="AL2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" s="17" t="s">
+      <c r="AM2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AN2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="17" t="s">
+      <c r="AO2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN2" s="17" t="s">
+    </row>
+    <row r="3" spans="1:41" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>84</v>
       </c>
+      <c r="B3" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="16"/>
+      <c r="AM3" s="16"/>
+      <c r="AN3" s="16"/>
+      <c r="AO3" s="16"/>
     </row>
-    <row r="3" spans="1:40" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
-      <c r="AH3" s="15"/>
-      <c r="AI3" s="15"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
+    <row r="4" spans="1:41" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
+        <v>2</v>
+      </c>
+      <c r="M4" s="4">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>4</v>
+      </c>
+      <c r="O4" s="4">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>7</v>
+      </c>
+      <c r="R4" s="4">
+        <v>8</v>
+      </c>
+      <c r="S4" s="4">
+        <v>9</v>
+      </c>
+      <c r="T4" s="4">
+        <v>10</v>
+      </c>
+      <c r="U4" s="4">
+        <v>11</v>
+      </c>
+      <c r="V4" s="4">
+        <v>12</v>
+      </c>
+      <c r="W4" s="4">
+        <v>13</v>
+      </c>
+      <c r="X4" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>15</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>16</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>17</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>18</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>19</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>20</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>21</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>22</v>
+      </c>
+      <c r="AG4" s="4">
+        <v>23</v>
+      </c>
+      <c r="AH4" s="4">
+        <v>24</v>
+      </c>
+      <c r="AI4" s="4">
+        <v>25</v>
+      </c>
+      <c r="AJ4" s="4">
+        <v>26</v>
+      </c>
+      <c r="AK4" s="4">
+        <v>27</v>
+      </c>
+      <c r="AL4" s="4">
+        <v>28</v>
+      </c>
+      <c r="AM4" s="4">
+        <v>29</v>
+      </c>
+      <c r="AN4" s="4">
+        <v>30</v>
+      </c>
+      <c r="AO4" s="4">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="1:40" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="4">
-        <v>1</v>
-      </c>
-      <c r="K4" s="4">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4">
-        <v>3</v>
-      </c>
-      <c r="M4" s="4">
-        <v>4</v>
-      </c>
-      <c r="N4" s="4">
-        <v>5</v>
-      </c>
-      <c r="O4" s="4">
-        <v>6</v>
-      </c>
-      <c r="P4" s="4">
-        <v>7</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>8</v>
-      </c>
-      <c r="R4" s="4">
-        <v>9</v>
-      </c>
-      <c r="S4" s="4">
-        <v>10</v>
-      </c>
-      <c r="T4" s="4">
-        <v>11</v>
-      </c>
-      <c r="U4" s="4">
-        <v>12</v>
-      </c>
-      <c r="V4" s="4">
-        <v>13</v>
-      </c>
-      <c r="W4" s="4">
-        <v>14</v>
-      </c>
-      <c r="X4" s="4">
-        <v>15</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>16</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>17</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>18</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>19</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>20</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>21</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>22</v>
-      </c>
-      <c r="AF4" s="4">
-        <v>23</v>
-      </c>
-      <c r="AG4" s="4">
-        <v>24</v>
-      </c>
-      <c r="AH4" s="4">
-        <v>25</v>
-      </c>
-      <c r="AI4" s="4">
-        <v>26</v>
-      </c>
-      <c r="AJ4" s="4">
-        <v>27</v>
-      </c>
-      <c r="AK4" s="4">
-        <v>28</v>
-      </c>
-      <c r="AL4" s="4">
-        <v>29</v>
-      </c>
-      <c r="AM4" s="4">
-        <v>30</v>
-      </c>
-      <c r="AN4" s="4">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>1</v>
@@ -1229,115 +1251,118 @@
         <v>2</v>
       </c>
       <c r="E5" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="J5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="K5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="L5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="M5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="N5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="O5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="P5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="Q5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="S5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="T5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="U5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="W5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="Y5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AC5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AB5" s="12" t="s">
+      <c r="AD5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AC5" s="12" t="s">
+      <c r="AE5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AD5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AE5" s="12" t="s">
+      <c r="AG5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AF5" s="12" t="s">
+      <c r="AH5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AG5" s="12" t="s">
+      <c r="AI5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AH5" s="12" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AI5" s="12" t="s">
+      <c r="AK5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AJ5" s="12" t="s">
+      <c r="AL5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AK5" s="12" t="s">
+      <c r="AM5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AL5" s="12" t="s">
+      <c r="AN5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AM5" s="12" t="s">
+      <c r="AO5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AN5" s="12" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1378,15 +1403,16 @@
       <c r="AL6" s="13"/>
       <c r="AM6" s="13"/>
       <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1424,15 +1450,16 @@
       <c r="AL7" s="7"/>
       <c r="AM7" s="7"/>
       <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -1470,15 +1497,16 @@
       <c r="AL8" s="7"/>
       <c r="AM8" s="7"/>
       <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1516,8 +1544,9 @@
       <c r="AL9" s="7"/>
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
+      <c r="AO9" s="7"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1558,15 +1587,16 @@
       <c r="AL10" s="7"/>
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
+      <c r="AO10" s="7"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -1604,15 +1634,16 @@
       <c r="AL11" s="7"/>
       <c r="AM11" s="7"/>
       <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -1650,15 +1681,16 @@
       <c r="AL12" s="7"/>
       <c r="AM12" s="7"/>
       <c r="AN12" s="7"/>
+      <c r="AO12" s="7"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -1696,18 +1728,20 @@
       <c r="AL13" s="7"/>
       <c r="AM13" s="7"/>
       <c r="AN13" s="7"/>
+      <c r="AO13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="G3:G4"/>
+  <mergeCells count="11">
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:AO3"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:AN3"/>
-    <mergeCell ref="H3:H4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="F3:F4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C269B7-C6AC-471F-9A5D-D34FE3735CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8109CA-09BE-4560-A9A5-9A2449E97D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8109CA-09BE-4560-A9A5-9A2449E97D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64595181-E4D6-40F8-B3D2-D9DAE3C66804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -370,6 +370,10 @@
   </si>
   <si>
     <t>{.unPostponeNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{changeCountLabel}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1596,7 +1600,7 @@
         <v>96</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64595181-E4D6-40F8-B3D2-D9DAE3C66804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F257FB-61C4-458F-9D71-A56FBBA86D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -374,6 +374,30 @@
   </si>
   <si>
     <t>{changeCountLabel}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{beginDay}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{endDay}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.beginDayA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.beginDay}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.endDayA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.endDay}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -885,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO13"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -893,11 +917,11 @@
     <col min="3" max="3" width="22.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="6" width="9.25" customWidth="1"/>
-    <col min="7" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="41" width="4.75" customWidth="1"/>
+    <col min="7" max="12" width="7.83203125" customWidth="1"/>
+    <col min="13" max="43" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -909,9 +933,9 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="6"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
@@ -930,7 +954,6 @@
         <v>99</v>
       </c>
       <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
@@ -940,13 +963,14 @@
         <v>100</v>
       </c>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
       <c r="AM1" s="7"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
     </row>
-    <row r="2" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>44</v>
       </c>
@@ -972,106 +996,112 @@
         <v>49</v>
       </c>
       <c r="I2" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="R2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="S2" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="T2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="V2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="W2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="X2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="Y2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Z2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="AA2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AE2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AG2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AH2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AI2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AH2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AK2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AL2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AK2" s="14" t="s">
+      <c r="AM2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AN2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AO2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AP2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AO2" s="14" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:41" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>84</v>
       </c>
@@ -1097,16 +1127,20 @@
         <v>89</v>
       </c>
       <c r="I3" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="L3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="M3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
       <c r="N3" s="16"/>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
@@ -1135,8 +1169,10 @@
       <c r="AM3" s="16"/>
       <c r="AN3" s="16"/>
       <c r="AO3" s="16"/>
+      <c r="AP3" s="16"/>
+      <c r="AQ3" s="16"/>
     </row>
-    <row r="4" spans="1:41" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1147,101 +1183,103 @@
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
-      <c r="K4" s="4">
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="4">
         <v>1</v>
       </c>
-      <c r="L4" s="4">
+      <c r="N4" s="4">
         <v>2</v>
       </c>
-      <c r="M4" s="4">
+      <c r="O4" s="4">
         <v>3</v>
       </c>
-      <c r="N4" s="4">
+      <c r="P4" s="4">
         <v>4</v>
       </c>
-      <c r="O4" s="4">
+      <c r="Q4" s="4">
         <v>5</v>
       </c>
-      <c r="P4" s="4">
+      <c r="R4" s="4">
         <v>6</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="S4" s="4">
         <v>7</v>
       </c>
-      <c r="R4" s="4">
+      <c r="T4" s="4">
         <v>8</v>
       </c>
-      <c r="S4" s="4">
+      <c r="U4" s="4">
         <v>9</v>
       </c>
-      <c r="T4" s="4">
+      <c r="V4" s="4">
         <v>10</v>
       </c>
-      <c r="U4" s="4">
+      <c r="W4" s="4">
         <v>11</v>
       </c>
-      <c r="V4" s="4">
+      <c r="X4" s="4">
         <v>12</v>
       </c>
-      <c r="W4" s="4">
+      <c r="Y4" s="4">
         <v>13</v>
       </c>
-      <c r="X4" s="4">
+      <c r="Z4" s="4">
         <v>14</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="AA4" s="4">
         <v>15</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="AB4" s="4">
         <v>16</v>
       </c>
-      <c r="AA4" s="4">
+      <c r="AC4" s="4">
         <v>17</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AD4" s="4">
         <v>18</v>
       </c>
-      <c r="AC4" s="4">
+      <c r="AE4" s="4">
         <v>19</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AF4" s="4">
         <v>20</v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AG4" s="4">
         <v>21</v>
       </c>
-      <c r="AF4" s="4">
+      <c r="AH4" s="4">
         <v>22</v>
       </c>
-      <c r="AG4" s="4">
+      <c r="AI4" s="4">
         <v>23</v>
       </c>
-      <c r="AH4" s="4">
+      <c r="AJ4" s="4">
         <v>24</v>
       </c>
-      <c r="AI4" s="4">
+      <c r="AK4" s="4">
         <v>25</v>
       </c>
-      <c r="AJ4" s="4">
+      <c r="AL4" s="4">
         <v>26</v>
       </c>
-      <c r="AK4" s="4">
+      <c r="AM4" s="4">
         <v>27</v>
       </c>
-      <c r="AL4" s="4">
+      <c r="AN4" s="4">
         <v>28</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AO4" s="4">
         <v>29</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AP4" s="4">
         <v>30</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AQ4" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -1267,106 +1305,112 @@
         <v>4</v>
       </c>
       <c r="I5" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="L5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="M5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="O5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="P5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="Q5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="S5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="T5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="U5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="W5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="Y5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AC5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AB5" s="12" t="s">
+      <c r="AD5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AC5" s="12" t="s">
+      <c r="AE5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AD5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AE5" s="12" t="s">
+      <c r="AG5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AF5" s="12" t="s">
+      <c r="AH5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AG5" s="12" t="s">
+      <c r="AI5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AH5" s="12" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AI5" s="12" t="s">
+      <c r="AK5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ5" s="12" t="s">
+      <c r="AL5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AK5" s="12" t="s">
+      <c r="AM5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AL5" s="12" t="s">
+      <c r="AN5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AM5" s="12" t="s">
+      <c r="AO5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AN5" s="12" t="s">
+      <c r="AP5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AO5" s="12" t="s">
+      <c r="AQ5" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1408,8 +1452,10 @@
       <c r="AM6" s="13"/>
       <c r="AN6" s="13"/>
       <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5" t="s">
@@ -1455,8 +1501,10 @@
       <c r="AM7" s="7"/>
       <c r="AN7" s="7"/>
       <c r="AO7" s="7"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
@@ -1502,8 +1550,10 @@
       <c r="AM8" s="7"/>
       <c r="AN8" s="7"/>
       <c r="AO8" s="7"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
@@ -1549,8 +1599,10 @@
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
+      <c r="AP9" s="7"/>
+      <c r="AQ9" s="7"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1592,8 +1644,10 @@
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
+      <c r="AP10" s="7"/>
+      <c r="AQ10" s="7"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
@@ -1639,8 +1693,10 @@
       <c r="AM11" s="7"/>
       <c r="AN11" s="7"/>
       <c r="AO11" s="7"/>
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="7"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10" t="s">
@@ -1686,8 +1742,10 @@
       <c r="AM12" s="7"/>
       <c r="AN12" s="7"/>
       <c r="AO12" s="7"/>
+      <c r="AP12" s="7"/>
+      <c r="AQ12" s="7"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="10" t="s">
@@ -1733,13 +1791,15 @@
       <c r="AM13" s="7"/>
       <c r="AN13" s="7"/>
       <c r="AO13" s="7"/>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:AO3"/>
-    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:AQ3"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -1747,6 +1807,8 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F257FB-61C4-458F-9D71-A56FBBA86D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E74F33D-DB9E-4968-9198-B070FEFFE902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t>{.endDay}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{heightQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.heightQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.heightQtyA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -909,19 +921,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AR13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="6" width="9.25" customWidth="1"/>
-    <col min="7" max="12" width="7.83203125" customWidth="1"/>
-    <col min="13" max="43" width="4.75" customWidth="1"/>
+    <col min="5" max="7" width="9.25" customWidth="1"/>
+    <col min="8" max="13" width="7.83203125" customWidth="1"/>
+    <col min="14" max="44" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -930,13 +942,13 @@
       <c r="D1" s="6"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="8"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="7"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="6"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
@@ -950,27 +962,28 @@
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="7"/>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AB1" s="7"/>
-      <c r="AD1" s="7"/>
+      <c r="AC1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
       <c r="AH1" s="7"/>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AJ1" s="7"/>
-      <c r="AL1" s="7"/>
+      <c r="AK1" s="7"/>
       <c r="AM1" s="7"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="7"/>
       <c r="AP1" s="7"/>
       <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
     </row>
-    <row r="2" spans="1:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>44</v>
       </c>
@@ -990,118 +1003,121 @@
         <v>104</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="R2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="S2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="T2" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="V2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="W2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="X2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Y2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="Z2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AA2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AE2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AG2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AH2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AH2" s="14" t="s">
+      <c r="AI2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AK2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AK2" s="14" t="s">
+      <c r="AL2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AM2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AN2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AO2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="14" t="s">
+      <c r="AP2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="14" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AR2" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:43" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>84</v>
       </c>
@@ -1121,27 +1137,29 @@
         <v>105</v>
       </c>
       <c r="G3" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="L3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="M3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="N3" s="16"/>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
       <c r="Q3" s="16"/>
@@ -1171,8 +1189,9 @@
       <c r="AO3" s="16"/>
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
+      <c r="AR3" s="16"/>
     </row>
-    <row r="4" spans="1:43" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1185,101 +1204,102 @@
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
-      <c r="M4" s="4">
+      <c r="M4" s="15"/>
+      <c r="N4" s="4">
         <v>1</v>
       </c>
-      <c r="N4" s="4">
+      <c r="O4" s="4">
         <v>2</v>
       </c>
-      <c r="O4" s="4">
+      <c r="P4" s="4">
         <v>3</v>
       </c>
-      <c r="P4" s="4">
+      <c r="Q4" s="4">
         <v>4</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="4">
         <v>5</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>6</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>7</v>
       </c>
-      <c r="T4" s="4">
+      <c r="U4" s="4">
         <v>8</v>
       </c>
-      <c r="U4" s="4">
+      <c r="V4" s="4">
         <v>9</v>
       </c>
-      <c r="V4" s="4">
+      <c r="W4" s="4">
         <v>10</v>
       </c>
-      <c r="W4" s="4">
+      <c r="X4" s="4">
         <v>11</v>
       </c>
-      <c r="X4" s="4">
+      <c r="Y4" s="4">
         <v>12</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="Z4" s="4">
         <v>13</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="AA4" s="4">
         <v>14</v>
       </c>
-      <c r="AA4" s="4">
+      <c r="AB4" s="4">
         <v>15</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AC4" s="4">
         <v>16</v>
       </c>
-      <c r="AC4" s="4">
+      <c r="AD4" s="4">
         <v>17</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AE4" s="4">
         <v>18</v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AF4" s="4">
         <v>19</v>
       </c>
-      <c r="AF4" s="4">
+      <c r="AG4" s="4">
         <v>20</v>
       </c>
-      <c r="AG4" s="4">
+      <c r="AH4" s="4">
         <v>21</v>
       </c>
-      <c r="AH4" s="4">
+      <c r="AI4" s="4">
         <v>22</v>
       </c>
-      <c r="AI4" s="4">
+      <c r="AJ4" s="4">
         <v>23</v>
       </c>
-      <c r="AJ4" s="4">
+      <c r="AK4" s="4">
         <v>24</v>
       </c>
-      <c r="AK4" s="4">
+      <c r="AL4" s="4">
         <v>25</v>
       </c>
-      <c r="AL4" s="4">
+      <c r="AM4" s="4">
         <v>26</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AN4" s="4">
         <v>27</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AO4" s="4">
         <v>28</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AP4" s="4">
         <v>29</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AQ4" s="4">
         <v>30</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AR4" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -1299,118 +1319,121 @@
         <v>106</v>
       </c>
       <c r="G5" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="I5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J5" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="L5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="M5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="N5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="O5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="P5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="Q5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="R5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="S5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="T5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="U5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="W5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="Y5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AB5" s="12" t="s">
+      <c r="AC5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AC5" s="12" t="s">
+      <c r="AD5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AD5" s="12" t="s">
+      <c r="AE5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AE5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AF5" s="12" t="s">
+      <c r="AG5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AG5" s="12" t="s">
+      <c r="AH5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AH5" s="12" t="s">
+      <c r="AI5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AI5" s="12" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AJ5" s="12" t="s">
+      <c r="AK5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AK5" s="12" t="s">
+      <c r="AL5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AL5" s="12" t="s">
+      <c r="AM5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AM5" s="12" t="s">
+      <c r="AN5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AN5" s="12" t="s">
+      <c r="AO5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AO5" s="12" t="s">
+      <c r="AP5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AP5" s="12" t="s">
+      <c r="AQ5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AQ5" s="12" t="s">
+      <c r="AR5" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1454,8 +1477,9 @@
       <c r="AO6" s="13"/>
       <c r="AP6" s="13"/>
       <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5" t="s">
@@ -1503,8 +1527,9 @@
       <c r="AO7" s="7"/>
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7"/>
+      <c r="AR7" s="7"/>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
@@ -1552,8 +1577,9 @@
       <c r="AO8" s="7"/>
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
@@ -1601,8 +1627,9 @@
       <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
+      <c r="AR9" s="7"/>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1646,8 +1673,9 @@
       <c r="AO10" s="7"/>
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
+      <c r="AR10" s="7"/>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
@@ -1695,8 +1723,9 @@
       <c r="AO11" s="7"/>
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7"/>
+      <c r="AR11" s="7"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10" t="s">
@@ -1744,8 +1773,9 @@
       <c r="AO12" s="7"/>
       <c r="AP12" s="7"/>
       <c r="AQ12" s="7"/>
+      <c r="AR12" s="7"/>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="10" t="s">
@@ -1793,22 +1823,24 @@
       <c r="AO13" s="7"/>
       <c r="AP13" s="7"/>
       <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="H3:H4"/>
+  <mergeCells count="14">
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:AR3"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:AQ3"/>
-    <mergeCell ref="K3:K4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/mpStructureAllocationExportTemp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\jy_aps\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E74F33D-DB9E-4968-9198-B070FEFFE902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1699BF11-9E39-4773-852B-CB2130C153AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="结构转产表" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="140">
   <si>
     <t>{.cxMachineCode}</t>
   </si>
@@ -411,6 +411,78 @@
   <si>
     <t>{.heightQtyA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDailyproductionQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay21}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay21A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay22A}</t>
+  </si>
+  <si>
+    <t>{.lastDay23A}</t>
+  </si>
+  <si>
+    <t>{.lastDay24A}</t>
+  </si>
+  <si>
+    <t>{.lastDay25A}</t>
+  </si>
+  <si>
+    <t>{.lastDay26A}</t>
+  </si>
+  <si>
+    <t>{.lastDay27A}</t>
+  </si>
+  <si>
+    <t>{.lastDay28A}</t>
+  </si>
+  <si>
+    <t>{.lastDay29A}</t>
+  </si>
+  <si>
+    <t>{.lastDay30A}</t>
+  </si>
+  <si>
+    <t>{.lastDay31A}</t>
+  </si>
+  <si>
+    <t>{.lastDay22}</t>
+  </si>
+  <si>
+    <t>{.lastDay23}</t>
+  </si>
+  <si>
+    <t>{.lastDay24}</t>
+  </si>
+  <si>
+    <t>{.lastDay25}</t>
+  </si>
+  <si>
+    <t>{.lastDay26}</t>
+  </si>
+  <si>
+    <t>{.lastDay27}</t>
+  </si>
+  <si>
+    <t>{.lastDay28}</t>
+  </si>
+  <si>
+    <t>{.lastDay29}</t>
+  </si>
+  <si>
+    <t>{.lastDay30}</t>
+  </si>
+  <si>
+    <t>{.lastDay31}</t>
   </si>
 </sst>
 </file>
@@ -518,7 +590,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -541,13 +613,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -600,6 +709,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -921,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR13"/>
+  <dimension ref="A1:BC13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -930,10 +1048,10 @@
     <col min="4" max="4" width="14.25" customWidth="1"/>
     <col min="5" max="7" width="9.25" customWidth="1"/>
     <col min="8" max="13" width="7.83203125" customWidth="1"/>
-    <col min="14" max="44" width="4.75" customWidth="1"/>
+    <col min="14" max="55" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:55" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -951,9 +1069,10 @@
       <c r="M1" s="6"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="P1" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
@@ -963,27 +1082,38 @@
       <c r="Y1" s="7"/>
       <c r="Z1" s="7"/>
       <c r="AA1" s="7"/>
-      <c r="AB1" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
       <c r="AG1" s="7"/>
       <c r="AH1" s="7"/>
       <c r="AI1" s="7"/>
-      <c r="AJ1" s="7" t="s">
-        <v>100</v>
-      </c>
+      <c r="AJ1" s="7"/>
       <c r="AK1" s="7"/>
-      <c r="AM1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
       <c r="AP1" s="7"/>
       <c r="AQ1" s="7"/>
       <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+      <c r="AT1" s="7"/>
+      <c r="AU1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
     </row>
-    <row r="2" spans="1:44" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>44</v>
       </c>
@@ -1024,100 +1154,133 @@
         <v>51</v>
       </c>
       <c r="N2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="Z2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="AA2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="AE2" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="AG2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="AH2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="AI2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AK2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AL2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AM2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AN2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AO2" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AP2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AR2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="AH2" s="14" t="s">
+      <c r="AS2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AT2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AU2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AK2" s="14" t="s">
+      <c r="AV2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AW2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AX2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AY2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AO2" s="14" t="s">
+      <c r="AZ2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="AP2" s="14" t="s">
+      <c r="BA2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="BB2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="AR2" s="14" t="s">
+      <c r="BC2" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:44" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:55" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>84</v>
       </c>
@@ -1157,20 +1320,22 @@
       <c r="M3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
       <c r="AA3" s="16"/>
       <c r="AB3" s="16"/>
@@ -1190,8 +1355,19 @@
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
       <c r="AR3" s="16"/>
+      <c r="AS3" s="16"/>
+      <c r="AT3" s="16"/>
+      <c r="AU3" s="16"/>
+      <c r="AV3" s="16"/>
+      <c r="AW3" s="16"/>
+      <c r="AX3" s="16"/>
+      <c r="AY3" s="16"/>
+      <c r="AZ3" s="16"/>
+      <c r="BA3" s="16"/>
+      <c r="BB3" s="16"/>
+      <c r="BC3" s="16"/>
     </row>
-    <row r="4" spans="1:44" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:55" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1206,100 +1382,133 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="4">
+        <v>21</v>
+      </c>
+      <c r="O4" s="4">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>24</v>
+      </c>
+      <c r="R4" s="4">
+        <v>25</v>
+      </c>
+      <c r="S4" s="4">
+        <v>26</v>
+      </c>
+      <c r="T4" s="4">
+        <v>27</v>
+      </c>
+      <c r="U4" s="4">
+        <v>28</v>
+      </c>
+      <c r="V4" s="4">
+        <v>29</v>
+      </c>
+      <c r="W4" s="4">
+        <v>30</v>
+      </c>
+      <c r="X4" s="4">
+        <v>31</v>
+      </c>
+      <c r="Y4" s="4">
         <v>1</v>
       </c>
-      <c r="O4" s="4">
+      <c r="Z4" s="4">
         <v>2</v>
       </c>
-      <c r="P4" s="4">
+      <c r="AA4" s="4">
         <v>3</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="AB4" s="4">
         <v>4</v>
       </c>
-      <c r="R4" s="4">
+      <c r="AC4" s="4">
         <v>5</v>
       </c>
-      <c r="S4" s="4">
+      <c r="AD4" s="4">
         <v>6</v>
       </c>
-      <c r="T4" s="4">
+      <c r="AE4" s="4">
         <v>7</v>
       </c>
-      <c r="U4" s="4">
+      <c r="AF4" s="4">
         <v>8</v>
       </c>
-      <c r="V4" s="4">
+      <c r="AG4" s="4">
         <v>9</v>
       </c>
-      <c r="W4" s="4">
+      <c r="AH4" s="4">
         <v>10</v>
       </c>
-      <c r="X4" s="4">
+      <c r="AI4" s="4">
         <v>11</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="AJ4" s="4">
         <v>12</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="AK4" s="4">
         <v>13</v>
       </c>
-      <c r="AA4" s="4">
+      <c r="AL4" s="4">
         <v>14</v>
       </c>
-      <c r="AB4" s="4">
+      <c r="AM4" s="4">
         <v>15</v>
       </c>
-      <c r="AC4" s="4">
+      <c r="AN4" s="4">
         <v>16</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AO4" s="4">
         <v>17</v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AP4" s="4">
         <v>18</v>
       </c>
-      <c r="AF4" s="4">
+      <c r="AQ4" s="4">
         <v>19</v>
       </c>
-      <c r="AG4" s="4">
+      <c r="AR4" s="4">
         <v>20</v>
       </c>
-      <c r="AH4" s="4">
+      <c r="AS4" s="4">
         <v>21</v>
       </c>
-      <c r="AI4" s="4">
+      <c r="AT4" s="4">
         <v>22</v>
       </c>
-      <c r="AJ4" s="4">
+      <c r="AU4" s="4">
         <v>23</v>
       </c>
-      <c r="AK4" s="4">
+      <c r="AV4" s="4">
         <v>24</v>
       </c>
-      <c r="AL4" s="4">
+      <c r="AW4" s="4">
         <v>25</v>
       </c>
-      <c r="AM4" s="4">
+      <c r="AX4" s="4">
         <v>26</v>
       </c>
-      <c r="AN4" s="4">
+      <c r="AY4" s="4">
         <v>27</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AZ4" s="4">
         <v>28</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="BA4" s="4">
         <v>29</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="BB4" s="4">
         <v>30</v>
       </c>
-      <c r="AR4" s="4">
+      <c r="BC4" s="4">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -1340,100 +1549,133 @@
         <v>6</v>
       </c>
       <c r="N5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="AC5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="AD5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="AE5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="AF5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="AG5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="AH5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="AI5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="AJ5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="AK5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AL5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AB5" s="12" t="s">
+      <c r="AM5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AC5" s="12" t="s">
+      <c r="AN5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AD5" s="12" t="s">
+      <c r="AO5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AE5" s="12" t="s">
+      <c r="AP5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AF5" s="12" t="s">
+      <c r="AQ5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AG5" s="12" t="s">
+      <c r="AR5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AH5" s="12" t="s">
+      <c r="AS5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AI5" s="12" t="s">
+      <c r="AT5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AJ5" s="12" t="s">
+      <c r="AU5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AK5" s="12" t="s">
+      <c r="AV5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AL5" s="12" t="s">
+      <c r="AW5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AM5" s="12" t="s">
+      <c r="AX5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AN5" s="12" t="s">
+      <c r="AY5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AO5" s="12" t="s">
+      <c r="AZ5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AP5" s="12" t="s">
+      <c r="BA5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="AQ5" s="12" t="s">
+      <c r="BB5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AR5" s="12" t="s">
+      <c r="BC5" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1478,8 +1720,19 @@
       <c r="AP6" s="13"/>
       <c r="AQ6" s="13"/>
       <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="5" t="s">
@@ -1528,8 +1781,19 @@
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7"/>
       <c r="AR7" s="7"/>
+      <c r="AS7" s="7"/>
+      <c r="AT7" s="7"/>
+      <c r="AU7" s="7"/>
+      <c r="AV7" s="7"/>
+      <c r="AW7" s="7"/>
+      <c r="AX7" s="7"/>
+      <c r="AY7" s="7"/>
+      <c r="AZ7" s="7"/>
+      <c r="BA7" s="7"/>
+      <c r="BB7" s="7"/>
+      <c r="BC7" s="7"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10" t="s">
@@ -1578,8 +1842,19 @@
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="7"/>
+      <c r="AU8" s="7"/>
+      <c r="AV8" s="7"/>
+      <c r="AW8" s="7"/>
+      <c r="AX8" s="7"/>
+      <c r="AY8" s="7"/>
+      <c r="AZ8" s="7"/>
+      <c r="BA8" s="7"/>
+      <c r="BB8" s="7"/>
+      <c r="BC8" s="7"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11" t="s">
@@ -1628,8 +1903,19 @@
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7"/>
+      <c r="AS9" s="7"/>
+      <c r="AT9" s="7"/>
+      <c r="AU9" s="7"/>
+      <c r="AV9" s="7"/>
+      <c r="AW9" s="7"/>
+      <c r="AX9" s="7"/>
+      <c r="AY9" s="7"/>
+      <c r="AZ9" s="7"/>
+      <c r="BA9" s="7"/>
+      <c r="BB9" s="7"/>
+      <c r="BC9" s="7"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1674,8 +1960,19 @@
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
+      <c r="AS10" s="7"/>
+      <c r="AT10" s="7"/>
+      <c r="AU10" s="7"/>
+      <c r="AV10" s="7"/>
+      <c r="AW10" s="7"/>
+      <c r="AX10" s="7"/>
+      <c r="AY10" s="7"/>
+      <c r="AZ10" s="7"/>
+      <c r="BA10" s="7"/>
+      <c r="BB10" s="7"/>
+      <c r="BC10" s="7"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
@@ -1724,8 +2021,19 @@
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="7"/>
+      <c r="AS11" s="7"/>
+      <c r="AT11" s="7"/>
+      <c r="AU11" s="7"/>
+      <c r="AV11" s="7"/>
+      <c r="AW11" s="7"/>
+      <c r="AX11" s="7"/>
+      <c r="AY11" s="7"/>
+      <c r="AZ11" s="7"/>
+      <c r="BA11" s="7"/>
+      <c r="BB11" s="7"/>
+      <c r="BC11" s="7"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="10" t="s">
@@ -1774,8 +2082,19 @@
       <c r="AP12" s="7"/>
       <c r="AQ12" s="7"/>
       <c r="AR12" s="7"/>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="7"/>
+      <c r="AU12" s="7"/>
+      <c r="AV12" s="7"/>
+      <c r="AW12" s="7"/>
+      <c r="AX12" s="7"/>
+      <c r="AY12" s="7"/>
+      <c r="AZ12" s="7"/>
+      <c r="BA12" s="7"/>
+      <c r="BB12" s="7"/>
+      <c r="BC12" s="7"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="10" t="s">
@@ -1824,12 +2143,23 @@
       <c r="AP13" s="7"/>
       <c r="AQ13" s="7"/>
       <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="7"/>
+      <c r="AU13" s="7"/>
+      <c r="AV13" s="7"/>
+      <c r="AW13" s="7"/>
+      <c r="AX13" s="7"/>
+      <c r="AY13" s="7"/>
+      <c r="AZ13" s="7"/>
+      <c r="BA13" s="7"/>
+      <c r="BB13" s="7"/>
+      <c r="BC13" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:AR3"/>
+    <mergeCell ref="Y3:BC3"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -1841,6 +2171,7 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="G3:G4"/>
+    <mergeCell ref="N3:X3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
